--- a/Base_Orcamentos.xlsx
+++ b/Base_Orcamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Orcamento\CONTROLE DE ORÇAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56A41EB1-451D-4E21-BABC-734F2F50F6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B41555C-4736-4B25-AD73-1966DF08BEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7F199963-AA89-4DB5-A57A-C933EA8FE225}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7A4315D1-B95F-4157-8BFB-14156F6ED1E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Orcamentos" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="453">
   <si>
     <t>Nº Orçamento</t>
   </si>
@@ -1389,6 +1389,15 @@
   </si>
   <si>
     <t>ETIQ 79mm X 95mm X 1 C | 45 M  c/ 450 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100601</t>
+  </si>
+  <si>
+    <t>ALTO VALE UNIFORMES LTDA</t>
+  </si>
+  <si>
+    <t>ETIQ 25mm X 40mm X 4 C | 43 M  c/ 4000 ETIQ</t>
   </si>
 </sst>
 </file>
@@ -1767,7 +1776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F004881-01AD-4D74-B43B-2F3EAF83542C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7B39E75-CF8A-4719-A26F-EB61362E87C2}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:X390"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1780,10 +1789,10 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1">
-        <v>277550.93000000005</v>
+        <v>301360.93000000005</v>
       </c>
       <c r="R1" s="1">
-        <v>1503082.0216666667</v>
+        <v>1506528.0216666667</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -8459,10 +8468,19 @@
         <v>0</v>
       </c>
       <c r="Q119" s="1">
-        <v>0</v>
+        <v>23810</v>
       </c>
       <c r="R119" s="3">
         <v>23810</v>
+      </c>
+      <c r="S119" t="s">
+        <v>263</v>
+      </c>
+      <c r="T119" t="s">
+        <v>44</v>
+      </c>
+      <c r="U119" t="s">
+        <v>94</v>
       </c>
       <c r="V119" s="2"/>
     </row>
@@ -12149,15 +12167,60 @@
       <c r="V184" s="2"/>
     </row>
     <row r="185" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B185" s="2"/>
-      <c r="I185" s="1"/>
-      <c r="J185" s="1"/>
-      <c r="L185" s="1"/>
-      <c r="M185" s="1"/>
-      <c r="O185" s="1"/>
-      <c r="P185" s="1"/>
-      <c r="Q185" s="1"/>
-      <c r="R185" s="1"/>
+      <c r="A185" t="s">
+        <v>450</v>
+      </c>
+      <c r="B185" s="2">
+        <v>46301.412546296298</v>
+      </c>
+      <c r="C185" t="s">
+        <v>451</v>
+      </c>
+      <c r="D185" t="s">
+        <v>26</v>
+      </c>
+      <c r="E185" t="s">
+        <v>261</v>
+      </c>
+      <c r="F185" t="s">
+        <v>452</v>
+      </c>
+      <c r="G185" t="s">
+        <v>33</v>
+      </c>
+      <c r="H185">
+        <v>80</v>
+      </c>
+      <c r="I185" s="3">
+        <v>33.54</v>
+      </c>
+      <c r="J185" s="3">
+        <v>2683.2</v>
+      </c>
+      <c r="K185">
+        <v>110</v>
+      </c>
+      <c r="L185" s="3">
+        <v>31.23</v>
+      </c>
+      <c r="M185" s="3">
+        <v>3435.3</v>
+      </c>
+      <c r="N185">
+        <v>150</v>
+      </c>
+      <c r="O185" s="3">
+        <v>28.13</v>
+      </c>
+      <c r="P185" s="3">
+        <v>4219.5</v>
+      </c>
+      <c r="Q185" s="1">
+        <v>0</v>
+      </c>
+      <c r="R185" s="1">
+        <v>3446</v>
+      </c>
       <c r="V185" s="2"/>
     </row>
     <row r="186" spans="1:22" x14ac:dyDescent="0.25">
